--- a/clients/1_Hamster/Hamster_assessment_results.xlsx
+++ b/clients/1_Hamster/Hamster_assessment_results.xlsx
@@ -4809,9 +4809,9 @@
   </sheetData>
   <mergeCells count="221">
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D53:D55"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="D60:D63"/>
+    <mergeCell ref="D53:D55"/>
     <mergeCell ref="F60:F63"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="G48:G49"/>

--- a/clients/1_Hamster/Hamster_assessment_results.xlsx
+++ b/clients/1_Hamster/Hamster_assessment_results.xlsx
@@ -8690,7 +8690,9 @@
           <t>1. Er bestaan gemeenschappelijke waarden en doelstellingen.</t>
         </is>
       </c>
-      <c r="C2" s="42" t="n"/>
+      <c r="C2" s="42" t="n">
+        <v>2</v>
+      </c>
       <c r="D2" s="138">
         <f>C6</f>
         <v/>
@@ -8712,7 +8714,9 @@
           <t>2. Onderlinge samenhang (wij-gevoel). Participatieve instelling, teamwork, het beste uit elkaar halen.</t>
         </is>
       </c>
-      <c r="C3" s="43" t="n"/>
+      <c r="C3" s="43" t="n">
+        <v>3</v>
+      </c>
       <c r="D3" s="117" t="n"/>
       <c r="E3" s="102" t="n"/>
       <c r="F3" s="102" t="n"/>
@@ -8723,7 +8727,9 @@
           <t>3. Klanten worden als partners beschouwd.</t>
         </is>
       </c>
-      <c r="C4" s="43" t="n"/>
+      <c r="C4" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="D4" s="117" t="n"/>
       <c r="E4" s="102" t="n"/>
       <c r="F4" s="102" t="n"/>
@@ -8734,7 +8740,9 @@
           <t>4. Regels en procedures zijn ondergeschikt aan het gevoel een team te zijn.</t>
         </is>
       </c>
-      <c r="C5" s="43" t="n"/>
+      <c r="C5" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="D5" s="117" t="n"/>
       <c r="E5" s="102" t="n"/>
       <c r="F5" s="102" t="n"/>
@@ -8758,7 +8766,9 @@
           <t>1. Snel reageren op snel veranderende omstandigheden.</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n"/>
+      <c r="C7" s="45" t="n">
+        <v>4</v>
+      </c>
       <c r="D7" s="142">
         <f>C11</f>
         <v/>
@@ -8773,7 +8783,9 @@
           <t>2. Centraal staan innovatie en vernieuwing zoals de ontwikkeling van nieuwe diensten en producten. Voorbereiding op de toekomst.</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n"/>
+      <c r="C8" s="45" t="n">
+        <v>3</v>
+      </c>
       <c r="D8" s="117" t="n"/>
       <c r="E8" s="130" t="inlineStr">
         <is>
@@ -8793,7 +8805,9 @@
           <t>3. Medewerkers worden gestimuleerd om creatief en flexibel te zijn.</t>
         </is>
       </c>
-      <c r="C9" s="45" t="n"/>
+      <c r="C9" s="45" t="n">
+        <v>2</v>
+      </c>
       <c r="D9" s="117" t="n"/>
       <c r="E9" s="102" t="n"/>
       <c r="F9" s="102" t="n"/>
@@ -8805,7 +8819,9 @@
           <t>4. De organisatie is flexibel en kan indien nodig snel een nieuwe vorm aannemen.</t>
         </is>
       </c>
-      <c r="C10" s="45" t="n"/>
+      <c r="C10" s="45" t="n">
+        <v>1</v>
+      </c>
       <c r="D10" s="117" t="n"/>
       <c r="E10" s="102" t="n"/>
       <c r="F10" s="102" t="n"/>
@@ -8830,7 +8846,9 @@
           <t>1. Het centraal staan van procedures en regels.</t>
         </is>
       </c>
-      <c r="C12" s="45" t="n"/>
+      <c r="C12" s="45" t="n">
+        <v>1</v>
+      </c>
       <c r="D12" s="142">
         <f>C16</f>
         <v/>
@@ -8845,7 +8863,9 @@
           <t>2. De leidinggevenden coördineren en organiseren.</t>
         </is>
       </c>
-      <c r="C13" s="45" t="n"/>
+      <c r="C13" s="45" t="n">
+        <v>2</v>
+      </c>
       <c r="D13" s="117" t="n"/>
       <c r="E13" s="130" t="inlineStr">
         <is>
@@ -8865,7 +8885,9 @@
           <t>3. Langetermijndoelen zijn stabiliteit (in stand houden van de organisatie), efficiëntie en voorspelbaarheid.</t>
         </is>
       </c>
-      <c r="C14" s="45" t="n"/>
+      <c r="C14" s="45" t="n">
+        <v>3</v>
+      </c>
       <c r="D14" s="117" t="n"/>
       <c r="E14" s="102" t="n"/>
       <c r="F14" s="102" t="n"/>
@@ -8877,7 +8899,9 @@
           <t>4. De organisatie kenmerkt zich door trage besluitvormingsprocessen</t>
         </is>
       </c>
-      <c r="C15" s="45" t="n"/>
+      <c r="C15" s="45" t="n">
+        <v>4</v>
+      </c>
       <c r="D15" s="117" t="n"/>
       <c r="E15" s="102" t="n"/>
       <c r="F15" s="102" t="n"/>
@@ -8902,7 +8926,9 @@
           <t>1. Centrale waarden zijn productiviteit, resultaten, winst en taakgerichtheid.</t>
         </is>
       </c>
-      <c r="C17" s="45" t="n"/>
+      <c r="C17" s="45" t="n">
+        <v>4</v>
+      </c>
       <c r="D17" s="142">
         <f>C21</f>
         <v/>
@@ -8917,7 +8943,9 @@
           <t>2. De externe positionering wordt benadrukt om de concurrentiepositie te versterken.</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
+      <c r="C18" s="45" t="n">
+        <v>3</v>
+      </c>
       <c r="D18" s="117" t="n"/>
       <c r="E18" s="130" t="inlineStr">
         <is>
@@ -8937,7 +8965,9 @@
           <t>3. Er is een duidelijk doel aanwezig en er wordt gebruikgemaakt van een agressieve strategie.</t>
         </is>
       </c>
-      <c r="C19" s="45" t="n"/>
+      <c r="C19" s="45" t="n">
+        <v>2</v>
+      </c>
       <c r="D19" s="117" t="n"/>
       <c r="E19" s="102" t="n"/>
       <c r="F19" s="102" t="n"/>
@@ -8949,7 +8979,9 @@
           <t>4. Leidinggevenden zijn veeleisend en leggen de nadruk op de marktleider zijn.</t>
         </is>
       </c>
-      <c r="C20" s="45" t="n"/>
+      <c r="C20" s="45" t="n">
+        <v>1</v>
+      </c>
       <c r="D20" s="117" t="n"/>
       <c r="E20" s="102" t="n"/>
       <c r="F20" s="102" t="n"/>
@@ -9125,7 +9157,11 @@
           <t>Hoe belangrijk vind je het dat je werk bestaat uit verschillende soorten activiteiten waarbij je diverse vaardigheden en talenten kunt inzetten en/of ontwikkelen? En wat zou voor jou een ideale verhouding zijn tussen afwisselende taken en meer routinematige werkzaamheden?</t>
         </is>
       </c>
-      <c r="D2" s="78" t="n"/>
+      <c r="D2" s="78" t="inlineStr">
+        <is>
+          <t>ds</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="14.4" customFormat="1" customHeight="1" s="133">
       <c r="A3" s="99" t="n"/>
@@ -9149,7 +9185,11 @@
           <t>Hoe belangrijk vind je het om in je werk betrokken te zijn bij een volledig proces of werkstuk, van begin tot eind, met een duidelijk zichtbaar resultaat? En in hoeverre zou je idealiter verantwoordelijk willen zijn voor het hele werkproces versus alleen een deel ervan?</t>
         </is>
       </c>
-      <c r="D4" s="78" t="n"/>
+      <c r="D4" s="78" t="inlineStr">
+        <is>
+          <t>dwd</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="14.4" customFormat="1" customHeight="1" s="133">
       <c r="A5" s="99" t="n"/>
@@ -9173,7 +9213,11 @@
           <t>Hoe belangrijk vind je het dat je werk een merkbare invloed heeft op het leven of welzijn van anderen, binnen en/of buiten de organisatie? En in welke mate zou je idealiter willen dat jouw werk impact heeft op anderen?</t>
         </is>
       </c>
-      <c r="D6" s="78" t="n"/>
+      <c r="D6" s="78" t="inlineStr">
+        <is>
+          <t>wdd</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="1" s="133">
       <c r="A7" s="84" t="n"/>
@@ -9197,7 +9241,11 @@
           <t>Hoe belangrijk vind je het om in je werk zelf te kunnen bepalen hoe en wanneer je taken uitvoert, zonder dat alles strak voorgeschreven is? En hoeveel vrijheid zou je idealiter willen hebben in het plannen en uitvoeren van je werk?</t>
         </is>
       </c>
-      <c r="D8" s="78" t="n"/>
+      <c r="D8" s="78" t="inlineStr">
+        <is>
+          <t>wdwad</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="14.4" customFormat="1" customHeight="1" s="133">
       <c r="A9" s="99" t="n"/>
@@ -9221,7 +9269,11 @@
           <t>Hoe belangrijk vind je het om duidelijke en bruikbare feedback te krijgen over hoe goed je je werk doet? En in welke mate zou je idealiter op de hoogte willen zijn van het effect van je werk en van punten waarop je jezelf kunt verbeteren?</t>
         </is>
       </c>
-      <c r="D10" s="78" t="n"/>
+      <c r="D10" s="78" t="inlineStr">
+        <is>
+          <t>wdada</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="1" s="133">
       <c r="A11" s="98" t="n"/>

--- a/clients/1_Hamster/Hamster_assessment_results.xlsx
+++ b/clients/1_Hamster/Hamster_assessment_results.xlsx
@@ -4809,9 +4809,9 @@
   </sheetData>
   <mergeCells count="221">
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E39:E40"/>
     <mergeCell ref="D60:D63"/>
     <mergeCell ref="D53:D55"/>
+    <mergeCell ref="E39:E40"/>
     <mergeCell ref="F60:F63"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="G48:G49"/>

--- a/clients/1_Hamster/Hamster_assessment_results.xlsx
+++ b/clients/1_Hamster/Hamster_assessment_results.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="5" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fase 1.0 | Loopbaanfasen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fase 1.1 | Big Five Dimensies" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Fase 2.0 | Loopbaanankers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Fase 2.1 | Carriere Clusters" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Fase 2.2 | Cultuur analyse" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Fase 2.3 | J.C.M." sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Rapport" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gegevens" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fase 1.0 | Loopbaanfasen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fase 1.1 | Big Five Dimensies" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fase 2.0 | Loopbaanankers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fase 2.1 | Carriere Clusters" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fase 2.2 | Cultuur analyse" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fase 2.3 | J.C.M." sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rapport" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gegevens" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -869,7 +869,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -887,24 +887,24 @@
       <nvPicPr>
         <cNvPr id="2" name="Afbeelding 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="1"/>
           <a:ext cx="1000125" cy="931366"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -915,7 +915,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
@@ -933,24 +933,24 @@
       <nvPicPr>
         <cNvPr id="3" name="Afbeelding 2" descr="BFP.jpg"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="8638760" y="10452652"/>
           <a:ext cx="6899414" cy="5441674"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -961,7 +961,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -979,24 +979,24 @@
       <nvPicPr>
         <cNvPr id="3" name="Afbeelding 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="3878580"/>
           <a:ext cx="5848350" cy="3867150"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1007,7 +1007,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -1025,24 +1025,24 @@
       <nvPicPr>
         <cNvPr id="2" name="Afbeelding 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="5090160"/>
           <a:ext cx="6461760" cy="4861560"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4809,9 +4809,9 @@
   </sheetData>
   <mergeCells count="221">
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E39:E40"/>
     <mergeCell ref="D60:D63"/>
     <mergeCell ref="D53:D55"/>
+    <mergeCell ref="E39:E40"/>
     <mergeCell ref="F60:F63"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="G48:G49"/>
@@ -5040,7 +5040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J200"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col width="52.5546875" bestFit="1" customWidth="1" style="128" min="1" max="1"/>
@@ -8540,6 +8540,75 @@
       <c r="I131" s="120" t="n"/>
       <c r="J131" s="121" t="n"/>
     </row>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
   </sheetData>
   <mergeCells count="83">
     <mergeCell ref="I100:I106"/>
@@ -9077,7 +9146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.88671875" bestFit="1" customWidth="1" style="113" min="1" max="1"/>
@@ -9226,6 +9295,45 @@
     <row r="11" customFormat="1" s="133">
       <c r="A11" s="98" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A9:B9"/>
@@ -9307,18 +9415,7 @@
           <t>Extraversie *</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>Hoge score op extraversie
-Als je hoog scoort op extraversie, straal je energie en enthousiasme uit in sociale omgevingen. Je zoekt graag gezelschap op, geniet van groepsactiviteiten en neemt vaak een leidende rol. Je hebt een voorkeur voor actieve en uitdagende situaties, bent assertief en houdt van nieuwe ervaringen. Dit zie je terug in de volgende eigenschappen:
-Hartelijkheid: Je maakt makkelijk contact en bent oprecht geïnteresseerd in anderen.
-Sociabiliteit: Je voelt je op je gemak in grote groepen en staat graag in het middelpunt van de aandacht.
-Dominantie: Je neemt het voortouw in gesprekken en beslissingen.
-Energie: Je hebt een constant hoog energieniveau en bent altijd in beweging.
-Avonturisme: Je zoekt spanning en avontuur op en houdt van nieuwe ervaringen.
-Vrolijkheid: Je hebt een opgewekt karakter en verspreidt positieve energie om je heen.</t>
-        </is>
-      </c>
+      <c r="B7" s="34" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="126" t="inlineStr">
@@ -9326,7 +9423,10 @@
           <t>Altruïsme *</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
+      <c r="B8" s="16">
+        <f>(20+C4-C9+C14-C19+C24-C29+C34-C39+C44-C49)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="85" t="inlineStr">
@@ -9334,7 +9434,10 @@
           <t>Consciëntieusheid *</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n"/>
+      <c r="B9" s="30">
+        <f>(14-D5+D10-D15+D20-D25+D30-D35+D40+D45+D50)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="83" t="inlineStr">
@@ -9342,7 +9445,10 @@
           <t>Neuroticisme *</t>
         </is>
       </c>
-      <c r="B10" s="77" t="n"/>
+      <c r="B10" s="77">
+        <f>(14+E6-E11+E16-E21+E26-E31+E36-E41+E46+E51)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="83" t="inlineStr">
@@ -9350,7 +9456,10 @@
           <t>Openheid *</t>
         </is>
       </c>
-      <c r="B11" s="77" t="n"/>
+      <c r="B11" s="77">
+        <f>(38-F7+F12-F17+F22-F27-F32-F37-F42-F47-F52)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="146" t="inlineStr">
@@ -9374,7 +9483,7 @@
           <t>Hoogste score 1 *</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n"/>
+      <c r="B14" s="34" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="126" t="inlineStr">
@@ -9382,7 +9491,7 @@
           <t>Hoogste score 2 *</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
+      <c r="B15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="146" t="inlineStr">
@@ -9406,7 +9515,7 @@
           <t>Hoogste score 1 *</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
+      <c r="B18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="126" t="inlineStr">
@@ -9414,7 +9523,7 @@
           <t>Hoogste score 2 *</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
+      <c r="B19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="144" t="inlineStr">
@@ -9438,7 +9547,7 @@
           <t>Hoogste score 1 *</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
+      <c r="B22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="126" t="inlineStr">
@@ -9493,11 +9602,7 @@
           <t>Taakvaardigheid</t>
         </is>
       </c>
-      <c r="B28" s="57" t="inlineStr">
-        <is>
-          <t>Dit is een test.</t>
-        </is>
-      </c>
+      <c r="B28" s="57" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="76" t="inlineStr">
@@ -9505,7 +9610,7 @@
           <t>Taakidentiteit</t>
         </is>
       </c>
-      <c r="B29" s="57" t="n"/>
+      <c r="B29" s="57" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="76" t="inlineStr">
@@ -9513,7 +9618,7 @@
           <t>Taakbetekenis</t>
         </is>
       </c>
-      <c r="B30" s="57" t="n"/>
+      <c r="B30" s="57" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="76" t="inlineStr">
@@ -9521,7 +9626,7 @@
           <t>Autonomie</t>
         </is>
       </c>
-      <c r="B31" s="57" t="n"/>
+      <c r="B31" s="57" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="76" t="inlineStr">
@@ -9529,7 +9634,7 @@
           <t>Feedback</t>
         </is>
       </c>
-      <c r="B32" s="57" t="n"/>
+      <c r="B32" s="57" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/clients/1_Hamster/Hamster_assessment_results.xlsx
+++ b/clients/1_Hamster/Hamster_assessment_results.xlsx
@@ -4809,9 +4809,9 @@
   </sheetData>
   <mergeCells count="221">
     <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E39:E40"/>
     <mergeCell ref="D60:D63"/>
     <mergeCell ref="D53:D55"/>
-    <mergeCell ref="E39:E40"/>
     <mergeCell ref="F60:F63"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="G48:G49"/>

--- a/clients/1_Hamster/Hamster_assessment_results.xlsx
+++ b/clients/1_Hamster/Hamster_assessment_results.xlsx
@@ -3214,7 +3214,9 @@
 </t>
         </is>
       </c>
-      <c r="C4" s="123" t="n"/>
+      <c r="C4" s="123" t="n">
+        <v>1</v>
+      </c>
       <c r="D4" s="123" t="n">
         <v>1</v>
       </c>
@@ -4809,9 +4811,9 @@
   </sheetData>
   <mergeCells count="221">
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E39:E40"/>
     <mergeCell ref="D60:D63"/>
     <mergeCell ref="D53:D55"/>
+    <mergeCell ref="E39:E40"/>
     <mergeCell ref="F60:F63"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="G48:G49"/>
